--- a/data/main/sheets/batch_06.xlsx
+++ b/data/main/sheets/batch_06.xlsx
@@ -467,17 +467,18 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_248</t>
+          <t xml:space="preserve">simple_python_313</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who invented the theory of relativity and in which year?</t>
+          <t xml:space="preserve">What's the total worth in euro of Messi according to latest data?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">invention_name = theory of relativity</t>
+          <t xml:space="preserve">name = Messi
+currency = euro</t>
         </is>
       </c>
       <c r="D3" s="6"/>
@@ -489,19 +490,18 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_146</t>
+          <t xml:space="preserve">simple_python_194</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find restaurants near me within 10 miles that offer Chinese cuisine in Seattle.</t>
+          <t xml:space="preserve">What are the top three plants suitable for a hill slope in terms of erosion prevention?</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Seattle
-cuisine = Chinese
-max_distance = 10</t>
+          <t xml:space="preserve">slope_type = hill
+num_results = three</t>
         </is>
       </c>
       <c r="D4" s="6"/>
@@ -513,19 +513,18 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_361</t>
+          <t xml:space="preserve">multiple_174</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find Italian restaurants near New York city that serves gluten-free options.</t>
+          <t xml:space="preserve">What is the ranking of Manchester United in Premier League?</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">city = New York city
-cuisine = Italian
-diet = gluten-free</t>
+          <t xml:space="preserve">team = Manchester United
+league = Premier League</t>
         </is>
       </c>
       <c r="D5" s="6"/>
@@ -537,17 +536,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_181</t>
+          <t xml:space="preserve">simple_python_365</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me the details of the last game played by Liverpool F.C. Include its statistics.</t>
+          <t xml:space="preserve">How many ounces in 2 pounds of butter?</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = Liverpool F.C.</t>
+          <t xml:space="preserve">quantity = 2
+from_unit = pounds
+to_unit = ounces
+item = butter</t>
         </is>
       </c>
       <c r="D6" s="6"/>
@@ -559,18 +561,18 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_330</t>
+          <t xml:space="preserve">multiple_89</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the average review rating and the age range for the board game 'Catan'?</t>
+          <t xml:space="preserve">Find a healthy lunch recipe under 500 calories that uses chicken and mushrooms.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game_name = Catan
-info_required = average review rating, age range</t>
+          <t xml:space="preserve">ingredients = chicken, mushrooms
+calories = 500</t>
         </is>
       </c>
       <c r="D7" s="6"/>
@@ -582,18 +584,19 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_36</t>
+          <t xml:space="preserve">simple_python_90</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the shortest driving distance between New York City and Washington D.C.</t>
+          <t xml:space="preserve">Retrieve Personal Info and Job History data of a specific employee whose ID is 345 in company 'ABC Ltd.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin = New York City
-destination = Washington D.C.</t>
+          <t xml:space="preserve">company_name = ABC Ltd.
+employee_id = 345
+data_field = Personal Info, Job History</t>
         </is>
       </c>
       <c r="D8" s="6"/>
@@ -605,19 +608,19 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_17</t>
+          <t xml:space="preserve">simple_python_207</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the conversion rate from Euro to Dollar at January 1, 2022</t>
+          <t xml:space="preserve">Get the shortest driving distance between New York, USA and Miami, USA.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_currency = Euro
-to_currency = Dollar
-date = January 1, 2022</t>
+          <t xml:space="preserve">start_location = New York, USA
+end_location = Miami, USA
+route_preference = shortest</t>
         </is>
       </c>
       <c r="D9" s="6"/>
@@ -629,17 +632,18 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_255</t>
+          <t xml:space="preserve">multiple_20</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the biography and main contributions of Pope Innocent III.</t>
+          <t xml:space="preserve">What is the price to commission a sculpture made of marble with a size of 3 feet?</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">papal_name = Pope Innocent III</t>
+          <t xml:space="preserve">material = marble
+size = 3</t>
         </is>
       </c>
       <c r="D10" s="6"/>
@@ -651,19 +655,18 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_90</t>
+          <t xml:space="preserve">simple_python_326</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I want a seafood restaurant in Seattle that can accommodate a group of 5.</t>
+          <t xml:space="preserve">Get the latest game score and statistics for Los Angeles Lakers in NBA.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Seattle
-cuisine = seafood
-group_size = 5</t>
+          <t xml:space="preserve">team_name = Los Angeles Lakers
+league = NBA</t>
         </is>
       </c>
       <c r="D11" s="6"/>
@@ -675,18 +678,18 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_313</t>
+          <t xml:space="preserve">multiple_24</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the total worth in euro of Messi according to latest data?</t>
+          <t xml:space="preserve">What is the fastest route from London to Edinburgh for playing a chess championship? Also provide an estimate of the distance.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">name = Messi
-currency = euro</t>
+          <t xml:space="preserve">start = London
+destination = Edinburgh</t>
         </is>
       </c>
       <c r="D12" s="6"/>
@@ -698,18 +701,19 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_194</t>
+          <t xml:space="preserve">simple_python_345</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the top three plants suitable for a hill slope in terms of erosion prevention?</t>
+          <t xml:space="preserve">Find the value of a vintage Super Mario Bros. game from 1985 like new.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">slope_type = hill
-num_results = three</t>
+          <t xml:space="preserve">game_name = Super Mario Bros.
+release_year = 1985
+condition = like new</t>
         </is>
       </c>
       <c r="D13" s="6"/>
@@ -721,18 +725,18 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_174</t>
+          <t xml:space="preserve">simple_python_197</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the ranking of Manchester United in Premier League?</t>
+          <t xml:space="preserve">Find the air quality index in San Diego at 12pm.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team = Manchester United
-league = Premier League</t>
+          <t xml:space="preserve">location = San Diego
+time = 12pm</t>
         </is>
       </c>
       <c r="D14" s="6"/>
@@ -744,20 +748,18 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_365</t>
+          <t xml:space="preserve">simple_python_350</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many ounces in 2 pounds of butter?</t>
+          <t xml:space="preserve">Get the highest scoring player of game 'Valorant' in 2022 season.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity = 2
-from_unit = pounds
-to_unit = ounces
-item = butter</t>
+          <t xml:space="preserve">game = Valorant
+season = 2022 season</t>
         </is>
       </c>
       <c r="D15" s="6"/>
@@ -769,18 +771,19 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_89</t>
+          <t xml:space="preserve">multiple_39</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a healthy lunch recipe under 500 calories that uses chicken and mushrooms.</t>
+          <t xml:space="preserve">Find a ride from New York to Philadelphia with maximum cost of $50</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ingredients = chicken, mushrooms
-calories = 500</t>
+          <t xml:space="preserve">source = New York
+destination = Philadelphia
+max_cost = 50</t>
         </is>
       </c>
       <c r="D16" s="6"/>
@@ -792,19 +795,19 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_378</t>
+          <t xml:space="preserve">simple_python_383</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert time 3pm from New York time zone to London time zone.</t>
+          <t xml:space="preserve">I would like to book a single room for two nights at The Plaza hotel.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">time = 3pm
-from_timezone = New York
-to_timezone = London</t>
+          <t xml:space="preserve">hotel_name = The Plaza
+room_type = single
+num_nights = two</t>
         </is>
       </c>
       <c r="D17" s="6"/>
@@ -816,19 +819,18 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_207</t>
+          <t xml:space="preserve">simple_python_308</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the shortest driving distance between New York, USA and Miami, USA.</t>
+          <t xml:space="preserve">What are the next five matches for Manchester United and who are they playing against in the English Premier League?</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_location = New York, USA
-end_location = Miami, USA
-route_preference = shortest</t>
+          <t xml:space="preserve">team_name = Manchester United
+num_matches = five</t>
         </is>
       </c>
       <c r="D18" s="6"/>
@@ -840,18 +842,19 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_20</t>
+          <t xml:space="preserve">multiple_13</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the price to commission a sculpture made of marble with a size of 3 feet?</t>
+          <t xml:space="preserve">How much revenue would company XYZ generate if we increase the sales units of product A by 10% while keeping the price the same?</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">material = marble
-size = 3</t>
+          <t xml:space="preserve">company = XYZ
+product = product A
+sales_units_increase_percentage = 10</t>
         </is>
       </c>
       <c r="D19" s="6"/>
@@ -863,19 +866,18 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_363</t>
+          <t xml:space="preserve">multiple_104</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the closest sushi restaurant with a patio in Boston.</t>
+          <t xml:space="preserve">Find the shortest driving distance between New York City and Washington D.C.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Boston
-cuisine = sushi
-amenities = patio</t>
+          <t xml:space="preserve">origin = New York City
+destination = Washington D.C.</t>
         </is>
       </c>
       <c r="D20" s="6"/>
@@ -887,18 +889,20 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_24</t>
+          <t xml:space="preserve">simple_python_110</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the fastest route from London to Edinburgh for playing a chess championship? Also provide an estimate of the distance.</t>
+          <t xml:space="preserve">Predict the price of the house in San Francisco with 3 bedrooms, 2 bathrooms and area of 1800 square feet.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start = London
-destination = Edinburgh</t>
+          <t xml:space="preserve">bedrooms = 3
+bathrooms = 2
+area = 1800
+location = San Francisco</t>
         </is>
       </c>
       <c r="D21" s="6"/>
@@ -910,19 +914,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_345</t>
+          <t xml:space="preserve">simple_python_209</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the value of a vintage Super Mario Bros. game from 1985 like new.</t>
+          <t xml:space="preserve">Locate the nearest public library in Boston, Massachusetts with English fiction section and free Wi-Fi.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game_name = Super Mario Bros.
-release_year = 1985
-condition = like new</t>
+          <t xml:space="preserve">location = Boston, Massachusetts
+facilities = fiction, Wi-Fi</t>
         </is>
       </c>
       <c r="D22" s="6"/>
@@ -934,18 +937,18 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_197</t>
+          <t xml:space="preserve">multiple_65</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the air quality index in San Diego at 12pm.</t>
+          <t xml:space="preserve">Find the distance between New York City and Los Angeles.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = San Diego
-time = 12pm</t>
+          <t xml:space="preserve">origin = New York City
+destination = Los Angeles</t>
         </is>
       </c>
       <c r="D23" s="6"/>
@@ -957,18 +960,19 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_199</t>
+          <t xml:space="preserve">simple_python_254</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predict the growth of forest in Yellowstone for the next 5 years including human impact.</t>
+          <t xml:space="preserve">Retrieve the historic dates and facts related to Christianity between year 300 and 400.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Yellowstone
-years = 5</t>
+          <t xml:space="preserve">religion = Christianity
+start_year = 300
+end_year = 400</t>
         </is>
       </c>
       <c r="D24" s="6"/>
@@ -980,18 +984,18 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_350</t>
+          <t xml:space="preserve">multiple_151</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the highest scoring player of game 'Valorant' in 2022 season.</t>
+          <t xml:space="preserve">Find the most followed person on twitter who tweets about psychology related to behaviour and group dynamics.</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game = Valorant
-season = 2022 season</t>
+          <t xml:space="preserve">topic = psychology
+sub_topics = behaviour, group dynamics</t>
         </is>
       </c>
       <c r="D25" s="6"/>
@@ -1003,19 +1007,18 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_39</t>
+          <t xml:space="preserve">simple_python_81</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a ride from New York to Philadelphia with maximum cost of $50</t>
+          <t xml:space="preserve">Find the fastest route from San Francisco to Los Angeles with toll roads avoided.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">source = New York
-destination = Philadelphia
-max_cost = 50</t>
+          <t xml:space="preserve">start_location = San Francisco
+end_location = Los Angeles</t>
         </is>
       </c>
       <c r="D26" s="6"/>
@@ -1027,19 +1030,19 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_383</t>
+          <t xml:space="preserve">simple_python_262</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I would like to book a single room for two nights at The Plaza hotel.</t>
+          <t xml:space="preserve">Change my painting's medium to oil and change size to 12x18 with red dominant color.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hotel_name = The Plaza
-room_type = single
-num_nights = two</t>
+          <t xml:space="preserve">size = 12x18
+medium = oil
+dominant_color = red</t>
         </is>
       </c>
       <c r="D27" s="6"/>
@@ -1051,18 +1054,18 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_308</t>
+          <t xml:space="preserve">multiple_55</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the next five matches for Manchester United and who are they playing against in the English Premier League?</t>
+          <t xml:space="preserve">Predict the stock price for Google for the next 3 days.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = Manchester United
-num_matches = five</t>
+          <t xml:space="preserve">company = Google
+days = 3</t>
         </is>
       </c>
       <c r="D28" s="6"/>
@@ -1074,19 +1077,18 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_13</t>
+          <t xml:space="preserve">simple_python_375</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much revenue would company XYZ generate if we increase the sales units of product A by 10% while keeping the price the same?</t>
+          <t xml:space="preserve">Check the total price for three pumpkins and two dozen eggs at Walmart.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company = XYZ
-product = product A
-sales_units_increase_percentage = 10</t>
+          <t xml:space="preserve">items = pumpkins, eggs
+quantities = three, two</t>
         </is>
       </c>
       <c r="D29" s="6"/>
@@ -1098,18 +1100,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_319</t>
+          <t xml:space="preserve">multiple_109</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the ranking of Manchester United in Premier League?</t>
+          <t xml:space="preserve">What are the names of proteins found in the plasma membrane?</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team = Manchester United
-league = Premier League</t>
+          <t xml:space="preserve">cell_compartment = plasma membrane</t>
         </is>
       </c>
       <c r="D30" s="6"/>
@@ -1121,18 +1122,17 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_104</t>
+          <t xml:space="preserve">simple_python_242</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the shortest driving distance between New York City and Washington D.C.</t>
+          <t xml:space="preserve">Who is the scientist that first proposed the theory of evolution?</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin = New York City
-destination = Washington D.C.</t>
+          <t xml:space="preserve">discovery = theory of evolution</t>
         </is>
       </c>
       <c r="D31" s="6"/>
@@ -1140,261 +1140,6 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="7"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_110</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predict the price of the house in San Francisco with 3 bedrooms, 2 bathrooms and area of 1800 square feet.</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bedrooms = 3
-bathrooms = 2
-area = 1800
-location = San Francisco</t>
-        </is>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_299</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What is the musical scale associated with C sharp major?</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key = C sharp</t>
-        </is>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_65</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find the distance between New York City and Los Angeles.</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">origin = New York City
-destination = Los Angeles</t>
-        </is>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_254</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Retrieve the historic dates and facts related to Christianity between year 300 and 400.</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">religion = Christianity
-start_year = 300
-end_year = 400</t>
-        </is>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_151</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find the most followed person on twitter who tweets about psychology related to behaviour and group dynamics.</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">topic = psychology
-sub_topics = behaviour, group dynamics</t>
-        </is>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_81</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find the fastest route from San Francisco to Los Angeles with toll roads avoided.</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_location = San Francisco
-end_location = Los Angeles</t>
-        </is>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_262</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Change my painting's medium to oil and change size to 12x18 with red dominant color.</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size = 12x18
-medium = oil
-dominant_color = red</t>
-        </is>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_55</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predict the stock price for Google for the next 3 days.</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company = Google
-days = 3</t>
-        </is>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_279</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What's the retail price of a Fender American Professional II Stratocaster in Rosewood Finish?</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand = Fender
-model = American Professional II Stratocaster
-finish = Rosewood</t>
-        </is>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_109</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What are the names of proteins found in the plasma membrane?</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cell_compartment = plasma membrane</t>
-        </is>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_242</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Who is the scientist that first proposed the theory of evolution?</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">discovery = theory of evolution</t>
-        </is>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="7"/>
     </row>
   </sheetData>
   <printOptions/>
